--- a/1_IR-Sensoren_Linearisierung.xlsx
+++ b/1_IR-Sensoren_Linearisierung.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\philipp\Documents\GitHub\autonom_car\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8B35891-54BE-4329-81BF-796AD0F3D07D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A076AD6-5F30-4AC6-BA8A-1B8F1CDE33BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{3FAD9BF2-B5AE-4568-AE41-C64B5EC617C1}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{3FAD9BF2-B5AE-4568-AE41-C64B5EC617C1}"/>
   </bookViews>
   <sheets>
     <sheet name="Front" sheetId="1" r:id="rId1"/>
+    <sheet name="Left" sheetId="2" r:id="rId2"/>
+    <sheet name="Right" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -36,12 +38,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="15">
   <si>
     <t>1 / (l+k)</t>
-  </si>
-  <si>
-    <t>k =</t>
   </si>
   <si>
     <t>d =</t>
@@ -68,19 +67,22 @@
     <t>=1/m</t>
   </si>
   <si>
-    <t>=m/d</t>
-  </si>
-  <si>
-    <t>y = Wert in Zentimeter</t>
-  </si>
-  <si>
     <t>x = ADC Wert</t>
   </si>
   <si>
-    <t>y = (m'  / (x + d')) - k</t>
+    <t>m'/(ADC + d') - k</t>
   </si>
   <si>
-    <t>m'/(ADC + d') - k</t>
+    <t>l = Wert in Zentimeter</t>
+  </si>
+  <si>
+    <t>=d/m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">k = </t>
+  </si>
+  <si>
+    <t>l = (m'  / (x + d')) - k</t>
   </si>
 </sst>
 </file>
@@ -122,10 +124,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -283,7 +286,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>460</c:v>
+                  <c:v>420</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>330</c:v>
@@ -623,12 +626,12 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Front!$B$2:$B$13</c:f>
+              <c:f>Front!$B$2:$B$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
-                  <c:v>460</c:v>
+                  <c:v>420</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>330</c:v>
@@ -662,51 +665,63 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>70</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Front!$C$2:$C$13</c:f>
+              <c:f>Front!$C$2:$C$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
-                  <c:v>3.3333333333333333E-2</c:v>
+                  <c:v>2.8571428571428571E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.5000000000000001E-2</c:v>
+                  <c:v>2.2222222222222223E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.02</c:v>
+                  <c:v>1.8181818181818181E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.6666666666666666E-2</c:v>
+                  <c:v>1.5384615384615385E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.4285714285714285E-2</c:v>
+                  <c:v>1.3333333333333334E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.2500000000000001E-2</c:v>
+                  <c:v>1.1764705882352941E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.1111111111111112E-2</c:v>
+                  <c:v>1.0526315789473684E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.01</c:v>
+                  <c:v>9.5238095238095247E-3</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9.0909090909090905E-3</c:v>
+                  <c:v>8.6956521739130436E-3</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>8.3333333333333332E-3</c:v>
+                  <c:v>8.0000000000000002E-3</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>7.6923076923076927E-3</c:v>
+                  <c:v>7.4074074074074077E-3</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>7.1428571428571426E-3</c:v>
+                  <c:v>6.8965517241379309E-3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>6.4516129032258064E-3</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>6.0606060606060606E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -758,12 +773,12 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Front!$B$2:$B$13</c:f>
+              <c:f>Front!$B$2:$B$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
-                  <c:v>460</c:v>
+                  <c:v>420</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>330</c:v>
@@ -797,51 +812,63 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>70</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Front!$D$2:$D$13</c:f>
+              <c:f>Front!$D$2:$D$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
-                  <c:v>3.5093167701863354E-2</c:v>
+                  <c:v>2.7676102699144171E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.5000000000000005E-2</c:v>
+                  <c:v>2.1887605482075526E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.1118012422360253E-2</c:v>
+                  <c:v>1.867177369481517E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.8788819875776401E-2</c:v>
+                  <c:v>1.6742274622458954E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.6459627329192549E-2</c:v>
+                  <c:v>1.4812775550102738E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.4130434782608697E-2</c:v>
+                  <c:v>1.2883276477746524E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.2577639751552796E-2</c:v>
+                  <c:v>1.159694376284238E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.1024844720496895E-2</c:v>
+                  <c:v>1.0310611047938236E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9.4720496894409936E-3</c:v>
+                  <c:v>9.0242783330340935E-3</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>8.6956521739130436E-3</c:v>
+                  <c:v>8.3811119755820215E-3</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>7.9192546583850935E-3</c:v>
+                  <c:v>7.7379456181299495E-3</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>7.1428571428571426E-3</c:v>
+                  <c:v>7.0947792606778784E-3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>6.4516129032258064E-3</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>5.1652801883216633E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -850,6 +877,1668 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-F959-4248-922E-0CB7EC643FE7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="492582432"/>
+        <c:axId val="484238208"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="492582432"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="484238208"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="484238208"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="492582432"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="de-DE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.7" r="0.7" t="0.78740157499999996" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="de-DE"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Left!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ADC Werte</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Left!$A$3:$A$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>80</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Left!$B$3:$B$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>268</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>197</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>148</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>75</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4F85-4B46-8552-527451A674C8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="492575712"/>
+        <c:axId val="484240688"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="492575712"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="484240688"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="484240688"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="492575712"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="de-DE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.7" r="0.7" t="0.78740157499999996" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="de-DE"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="de-AT"/>
+              <a:t>Näherungsgerade</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Left!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1 / (l+k)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Left!$B$3:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>268</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>197</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>148</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>75</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Left!$C$3:$C$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.8571428571428571E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.2222222222222223E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.8181818181818181E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.5384615384615385E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.3333333333333334E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.1764705882352941E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D3A0-4EFE-BEB3-61D859D5705B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Left!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>m*ADC+d</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Left!$B$3:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>268</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>197</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>148</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>75</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Left!$D$3:$D$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>3.9777845507805887E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.9390768397168886E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.2222222222222223E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.8125910122252703E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.5199972907988758E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.30055199972908E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.1542551390158829E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-D3A0-4EFE-BEB3-61D859D5705B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="492582432"/>
+        <c:axId val="484238208"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="492582432"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="484238208"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="484238208"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="492582432"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="de-DE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.7" r="0.7" t="0.78740157499999996" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="de-DE"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Right!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ADC Werte</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Right!$A$3:$A$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>80</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Right!$B$3:$B$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>273</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>202</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>119</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>98</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>88</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>74</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-F15A-496E-ACA9-ED084F8E7E56}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="492575712"/>
+        <c:axId val="484240688"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="492575712"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="484240688"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="484240688"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="492575712"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="de-DE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.7" r="0.7" t="0.78740157499999996" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="de-DE"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="de-AT"/>
+              <a:t>Näherungsgerade</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Right!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1 / (l+k)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Right!$B$3:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>273</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>202</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>119</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>98</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>88</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>74</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Right!$C$3:$C$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>3.7037037037037035E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.7027027027027029E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.1276595744680851E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.7543859649122806E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.4925373134328358E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.2987012987012988E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.1494252873563218E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4826-4356-9F11-6780923E0CE8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Right!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>m*ADC+d</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Right!$B$3:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>273</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>202</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>119</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>98</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>88</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>74</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Right!$D$3:$D$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>3.7064346760295325E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.7951092109005666E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.1276595744680851E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.7297569065948745E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.4602099380356033E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.3318542387216645E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.1521562596821503E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-4826-4356-9F11-6780923E0CE8}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1144,6 +2833,166 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -1661,6 +3510,2070 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -2237,6 +6150,168 @@
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>126366</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>40323</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>227240</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>28077</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Diagramm 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5233B73F-4E9E-4532-8839-ABFA4A54F1A9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>137086</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>470</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>103615</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Diagramm 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C046122-FD79-4FCE-B742-962D90A79180}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>126366</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>40323</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>227240</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>28077</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Diagramm 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E313206A-826A-4F4A-A9D4-38E2AF2FB47F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>137086</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>470</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>103615</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Diagramm 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EFF9C7BE-4B39-4102-A2B4-9C0EA532E95C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -2579,19 +6654,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
       </c>
       <c r="D1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.45">
@@ -2599,19 +6674,19 @@
         <v>20</v>
       </c>
       <c r="B2" s="2">
-        <v>460</v>
+        <v>420</v>
       </c>
       <c r="C2">
-        <f t="shared" ref="C2:C15" si="0">1/(A2+$D$18)</f>
-        <v>3.3333333333333333E-2</v>
+        <f>1/(A2+$D$18)</f>
+        <v>2.8571428571428571E-2</v>
       </c>
       <c r="D2">
-        <f t="shared" ref="D2:D15" si="1">$D$19*B2+$D$20</f>
-        <v>3.5093167701863354E-2</v>
+        <f t="shared" ref="D2:D15" si="0">$D$19*B2+$D$20</f>
+        <v>2.7676102699144171E-2</v>
       </c>
       <c r="E2">
         <f>$D$21/(B2+$D$22)-$D$18</f>
-        <v>18.495575221238933</v>
+        <v>21.132254995242626</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
@@ -2622,16 +6697,16 @@
         <v>330</v>
       </c>
       <c r="C3">
+        <f t="shared" ref="C2:C15" si="1">1/(A3+$D$18)</f>
+        <v>2.2222222222222223E-2</v>
+      </c>
+      <c r="D3">
         <f t="shared" si="0"/>
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="D3">
-        <f t="shared" si="1"/>
-        <v>2.5000000000000005E-2</v>
+        <v>2.1887605482075526E-2</v>
       </c>
       <c r="E3">
         <f t="shared" ref="E3:E10" si="2">$D$21/(B3+$D$22)-$D$18</f>
-        <v>29.999999999999993</v>
+        <v>30.687958000656238</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
@@ -2642,16 +6717,16 @@
         <v>280</v>
       </c>
       <c r="C4">
+        <f t="shared" si="1"/>
+        <v>1.8181818181818181E-2</v>
+      </c>
+      <c r="D4">
         <f t="shared" si="0"/>
-        <v>0.02</v>
-      </c>
-      <c r="D4">
-        <f t="shared" si="1"/>
-        <v>2.1118012422360253E-2</v>
+        <v>1.867177369481517E-2</v>
       </c>
       <c r="E4">
         <f t="shared" si="2"/>
-        <v>37.35294117647058</v>
+        <v>38.556775930595322</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
@@ -2662,16 +6737,16 @@
         <v>250</v>
       </c>
       <c r="C5">
+        <f t="shared" si="1"/>
+        <v>1.5384615384615385E-2</v>
+      </c>
+      <c r="D5">
         <f t="shared" si="0"/>
-        <v>1.6666666666666666E-2</v>
-      </c>
-      <c r="D5">
-        <f t="shared" si="1"/>
-        <v>1.8788819875776401E-2</v>
+        <v>1.6742274622458954E-2</v>
       </c>
       <c r="E5">
         <f t="shared" si="2"/>
-        <v>43.223140495867767</v>
+        <v>44.729040560507123</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
@@ -2682,16 +6757,16 @@
         <v>220</v>
       </c>
       <c r="C6">
+        <f t="shared" si="1"/>
+        <v>1.3333333333333334E-2</v>
+      </c>
+      <c r="D6">
         <f t="shared" si="0"/>
-        <v>1.4285714285714285E-2</v>
-      </c>
-      <c r="D6">
-        <f t="shared" si="1"/>
-        <v>1.6459627329192549E-2</v>
+        <v>1.4812775550102738E-2</v>
       </c>
       <c r="E6">
         <f t="shared" si="2"/>
-        <v>50.754716981132077</v>
+        <v>52.509292678985076</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
@@ -2702,16 +6777,16 @@
         <v>190</v>
       </c>
       <c r="C7">
+        <f t="shared" si="1"/>
+        <v>1.1764705882352941E-2</v>
+      </c>
+      <c r="D7">
         <f t="shared" si="0"/>
-        <v>1.2500000000000001E-2</v>
-      </c>
-      <c r="D7">
-        <f t="shared" si="1"/>
-        <v>1.4130434782608697E-2</v>
+        <v>1.2883276477746524E-2</v>
       </c>
       <c r="E7">
         <f t="shared" si="2"/>
-        <v>60.769230769230774</v>
+        <v>62.620006193868079</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.45">
@@ -2722,16 +6797,16 @@
         <v>170</v>
       </c>
       <c r="C8">
+        <f t="shared" si="1"/>
+        <v>1.0526315789473684E-2</v>
+      </c>
+      <c r="D8">
         <f t="shared" si="0"/>
-        <v>1.1111111111111112E-2</v>
-      </c>
-      <c r="D8">
-        <f t="shared" si="1"/>
-        <v>1.2577639751552796E-2</v>
+        <v>1.159694376284238E-2</v>
       </c>
       <c r="E8">
         <f t="shared" si="2"/>
-        <v>69.506172839506178</v>
+        <v>71.229615358150426</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.45">
@@ -2742,16 +6817,16 @@
         <v>150</v>
       </c>
       <c r="C9">
+        <f t="shared" si="1"/>
+        <v>9.5238095238095247E-3</v>
+      </c>
+      <c r="D9">
         <f t="shared" si="0"/>
-        <v>0.01</v>
-      </c>
-      <c r="D9">
-        <f t="shared" si="1"/>
-        <v>1.1024844720496895E-2</v>
+        <v>1.0310611047938236E-2</v>
       </c>
       <c r="E9">
         <f t="shared" si="2"/>
-        <v>80.704225352112687</v>
+        <v>81.987462270722091</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
@@ -2763,15 +6838,15 @@
       </c>
       <c r="C10">
         <f>1/(A10+$D$18)</f>
-        <v>9.0909090909090905E-3</v>
+        <v>8.6956521739130436E-3</v>
       </c>
       <c r="D10">
-        <f t="shared" si="1"/>
-        <v>9.4720496894409936E-3</v>
+        <f t="shared" si="0"/>
+        <v>9.0242783330340935E-3</v>
       </c>
       <c r="E10">
         <f t="shared" si="2"/>
-        <v>95.573770491803288</v>
+        <v>95.812184985409857</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
@@ -2782,16 +6857,16 @@
         <v>120</v>
       </c>
       <c r="C11">
+        <f t="shared" si="1"/>
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="D11">
         <f t="shared" si="0"/>
-        <v>8.3333333333333332E-3</v>
-      </c>
-      <c r="D11">
-        <f t="shared" si="1"/>
-        <v>8.6956521739130436E-3</v>
+        <v>8.3811119755820215E-3</v>
       </c>
       <c r="E11">
         <f>$D$21/(B11+$D$22)-$D$18</f>
-        <v>105.00000000000001</v>
+        <v>104.31590974007428</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
@@ -2802,16 +6877,16 @@
         <v>110</v>
       </c>
       <c r="C12">
+        <f t="shared" si="1"/>
+        <v>7.4074074074074077E-3</v>
+      </c>
+      <c r="D12">
         <f t="shared" si="0"/>
-        <v>7.6923076923076927E-3</v>
-      </c>
-      <c r="D12">
-        <f t="shared" si="1"/>
-        <v>7.9192546583850935E-3</v>
+        <v>7.7379456181299495E-3</v>
       </c>
       <c r="E12">
         <f t="shared" ref="E12:E15" si="3">$D$21/(B12+$D$22)-$D$18</f>
-        <v>116.27450980392159</v>
+        <v>114.23326802103745</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.45">
@@ -2822,16 +6897,16 @@
         <v>100</v>
       </c>
       <c r="C13">
+        <f t="shared" si="1"/>
+        <v>6.8965517241379309E-3</v>
+      </c>
+      <c r="D13">
         <f t="shared" si="0"/>
-        <v>7.1428571428571426E-3</v>
-      </c>
-      <c r="D13">
-        <f t="shared" si="1"/>
-        <v>7.1428571428571426E-3</v>
+        <v>7.0947792606778784E-3</v>
       </c>
       <c r="E13">
         <f t="shared" si="3"/>
-        <v>130.00000000000003</v>
+        <v>125.94871218085706</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.45">
@@ -2842,16 +6917,16 @@
         <v>90</v>
       </c>
       <c r="C14">
+        <f t="shared" si="1"/>
+        <v>6.4516129032258064E-3</v>
+      </c>
+      <c r="D14">
         <f t="shared" si="0"/>
-        <v>6.6666666666666671E-3</v>
-      </c>
-      <c r="D14">
-        <f t="shared" si="1"/>
-        <v>6.3664596273291917E-3</v>
+        <v>6.4516129032258064E-3</v>
       </c>
       <c r="E14">
         <f t="shared" si="3"/>
-        <v>147.07317073170734</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.45">
@@ -2859,74 +6934,74 @@
         <v>150</v>
       </c>
       <c r="B15" s="2">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="C15">
+        <f t="shared" si="1"/>
+        <v>6.0606060606060606E-3</v>
+      </c>
+      <c r="D15">
         <f t="shared" si="0"/>
-        <v>6.2500000000000003E-3</v>
-      </c>
-      <c r="D15">
-        <f t="shared" si="1"/>
-        <v>4.0372670807453407E-3</v>
+        <v>5.1652801883216633E-3</v>
       </c>
       <c r="E15">
         <f t="shared" si="3"/>
-        <v>237.69230769230776</v>
+        <v>178.60033987331997</v>
       </c>
     </row>
     <row r="18" spans="3:5" x14ac:dyDescent="0.45">
       <c r="C18" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D18" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="3:5" x14ac:dyDescent="0.45">
       <c r="C19" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D19">
-        <f>(C3-C13)/(B3-B13)</f>
-        <v>7.7639751552795047E-5</v>
+        <f>(C2-C15)/(B2-B15)</f>
+        <v>6.4316635745207169E-5</v>
       </c>
     </row>
     <row r="20" spans="3:5" x14ac:dyDescent="0.45">
       <c r="C20" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20">
-        <f>C13-(D19*B13)</f>
-        <v>-6.2111801242236211E-4</v>
+        <f>C14-(D19*B14)</f>
+        <v>6.6311568615716118E-4</v>
       </c>
     </row>
     <row r="21" spans="3:5" x14ac:dyDescent="0.45">
       <c r="C21" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D21">
         <f>1/D19</f>
-        <v>12879.999999999998</v>
+        <v>15548.076923076924</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="3:5" x14ac:dyDescent="0.45">
       <c r="C22" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D22">
         <f>D20/D19</f>
-        <v>-8.0000000000000231</v>
+        <v>10.310173697270478</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="3:5" x14ac:dyDescent="0.45">
       <c r="C24" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="3:5" x14ac:dyDescent="0.45">
@@ -2936,7 +7011,559 @@
     </row>
     <row r="26" spans="3:5" x14ac:dyDescent="0.45">
       <c r="C26" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61CE9AF4-45C1-48AA-A6E4-B41FA3D4565F}">
+  <dimension ref="A1:E26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="4" max="4" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A2">
+        <v>10</v>
+      </c>
+      <c r="B2">
+        <v>500</v>
+      </c>
+      <c r="C2">
+        <f>1/(A2+$D$18)</f>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="D2">
+        <f>$D$19*B2+$D$20</f>
+        <v>7.3718717193267641E-2</v>
+      </c>
+      <c r="E2">
+        <f>$D$21/(B2+$D$22)-$D$18</f>
+        <v>8.5650759816982411</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A3">
+        <v>20</v>
+      </c>
+      <c r="B3">
+        <v>268</v>
+      </c>
+      <c r="C3">
+        <f>1/(A3+$D$18)</f>
+        <v>0.04</v>
+      </c>
+      <c r="D3">
+        <f>$D$19*B3+$D$20</f>
+        <v>3.9777845507805887E-2</v>
+      </c>
+      <c r="E3">
+        <f>$D$21/(B3+$D$22)-$D$18</f>
+        <v>20.139621998978377</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A4">
+        <v>30</v>
+      </c>
+      <c r="B4">
+        <v>197</v>
+      </c>
+      <c r="C4">
+        <f>1/(A4+$D$18)</f>
+        <v>2.8571428571428571E-2</v>
+      </c>
+      <c r="D4">
+        <f>$D$19*B4+$D$20</f>
+        <v>2.9390768397168886E-2</v>
+      </c>
+      <c r="E4">
+        <f>$D$21/(B4+$D$22)-$D$18</f>
+        <v>29.024289072221968</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A5">
+        <v>40</v>
+      </c>
+      <c r="B5">
+        <v>148</v>
+      </c>
+      <c r="C5">
+        <f>1/(A5+$D$18)</f>
+        <v>2.2222222222222223E-2</v>
+      </c>
+      <c r="D5">
+        <f>$D$19*B5+$D$20</f>
+        <v>2.2222222222222223E-2</v>
+      </c>
+      <c r="E5">
+        <f>$D$21/(B5+$D$22)-$D$18</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A6">
+        <v>50</v>
+      </c>
+      <c r="B6">
+        <v>120</v>
+      </c>
+      <c r="C6">
+        <f>1/(A6+$D$18)</f>
+        <v>1.8181818181818181E-2</v>
+      </c>
+      <c r="D6">
+        <f>$D$19*B6+$D$20</f>
+        <v>1.8125910122252703E-2</v>
+      </c>
+      <c r="E6">
+        <f>$D$21/(B6+$D$22)-$D$18</f>
+        <v>50.169643524400264</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A7">
+        <v>60</v>
+      </c>
+      <c r="B7">
+        <v>100</v>
+      </c>
+      <c r="C7">
+        <f>1/(A7+$D$18)</f>
+        <v>1.5384615384615385E-2</v>
+      </c>
+      <c r="D7">
+        <f>$D$19*B7+$D$20</f>
+        <v>1.5199972907988758E-2</v>
+      </c>
+      <c r="E7">
+        <f>$D$21/(B7+$D$22)-$D$18</f>
+        <v>60.789590945548511</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A8">
+        <v>70</v>
+      </c>
+      <c r="B8">
+        <v>85</v>
+      </c>
+      <c r="C8">
+        <f>1/(A8+$D$18)</f>
+        <v>1.3333333333333334E-2</v>
+      </c>
+      <c r="D8">
+        <f>$D$19*B8+$D$20</f>
+        <v>1.30055199972908E-2</v>
+      </c>
+      <c r="E8">
+        <f>$D$21/(B8+$D$22)-$D$18</f>
+        <v>71.890428080408284</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A9">
+        <v>80</v>
+      </c>
+      <c r="B9">
+        <v>75</v>
+      </c>
+      <c r="C9">
+        <f>1/(A9+$D$18)</f>
+        <v>1.1764705882352941E-2</v>
+      </c>
+      <c r="D9">
+        <f>$D$19*B9+$D$20</f>
+        <v>1.1542551390158829E-2</v>
+      </c>
+      <c r="E9">
+        <f>$D$21/(B9+$D$22)-$D$18</f>
+        <v>81.635958220866073</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B10" s="3"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B11" s="3"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B12" s="3"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B13" s="3"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B14" s="3"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B15" s="3"/>
+    </row>
+    <row r="18" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C19" t="s">
+        <v>2</v>
+      </c>
+      <c r="D19">
+        <f>(C3-C9)/(B3-B9)</f>
+        <v>1.4629686071319719E-4</v>
+      </c>
+    </row>
+    <row r="20" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C20" t="s">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <f>C5-(D19*B5)</f>
+        <v>5.7028683666903932E-4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C21" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21">
+        <f>1/D19</f>
+        <v>6835.416666666667</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C22" t="s">
+        <v>5</v>
+      </c>
+      <c r="D22">
+        <f>D20/D19</f>
+        <v>3.8981481481481626</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C24" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C26" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E7F75AF-5683-4D09-B045-23F9AA665E89}">
+  <dimension ref="A1:E26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="4" max="4" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A2">
+        <v>10</v>
+      </c>
+      <c r="B2">
+        <v>495</v>
+      </c>
+      <c r="C2">
+        <f>1/(A2+$D$18)</f>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="D2">
+        <f>$D$19*B2+$D$20</f>
+        <v>6.5559312007989742E-2</v>
+      </c>
+      <c r="E2">
+        <f>$D$21/(B2+$D$22)-$D$18</f>
+        <v>8.2533632427095913</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A3">
+        <v>20</v>
+      </c>
+      <c r="B3">
+        <v>273</v>
+      </c>
+      <c r="C3">
+        <f>1/(A3+$D$18)</f>
+        <v>3.7037037037037035E-2</v>
+      </c>
+      <c r="D3">
+        <f>$D$19*B3+$D$20</f>
+        <v>3.7064346760295325E-2</v>
+      </c>
+      <c r="E3">
+        <f>$D$21/(B3+$D$22)-$D$18</f>
+        <v>19.980105880922647</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A4">
+        <v>30</v>
+      </c>
+      <c r="B4">
+        <v>202</v>
+      </c>
+      <c r="C4">
+        <f>1/(A4+$D$18)</f>
+        <v>2.7027027027027029E-2</v>
+      </c>
+      <c r="D4">
+        <f>$D$19*B4+$D$20</f>
+        <v>2.7951092109005666E-2</v>
+      </c>
+      <c r="E4">
+        <f>$D$21/(B4+$D$22)-$D$18</f>
+        <v>28.776777383156571</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A5">
+        <v>40</v>
+      </c>
+      <c r="B5">
+        <v>150</v>
+      </c>
+      <c r="C5">
+        <f>1/(A5+$D$18)</f>
+        <v>2.1276595744680851E-2</v>
+      </c>
+      <c r="D5">
+        <f>$D$19*B5+$D$20</f>
+        <v>2.1276595744680851E-2</v>
+      </c>
+      <c r="E5">
+        <f>$D$21/(B5+$D$22)-$D$18</f>
+        <v>40.000000000000007</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A6">
+        <v>50</v>
+      </c>
+      <c r="B6">
+        <v>119</v>
+      </c>
+      <c r="C6">
+        <f>1/(A6+$D$18)</f>
+        <v>1.7543859649122806E-2</v>
+      </c>
+      <c r="D6">
+        <f>$D$19*B6+$D$20</f>
+        <v>1.7297569065948745E-2</v>
+      </c>
+      <c r="E6">
+        <f>$D$21/(B6+$D$22)-$D$18</f>
+        <v>50.811591685941423</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A7">
+        <v>60</v>
+      </c>
+      <c r="B7">
+        <v>98</v>
+      </c>
+      <c r="C7">
+        <f>1/(A7+$D$18)</f>
+        <v>1.4925373134328358E-2</v>
+      </c>
+      <c r="D7">
+        <f>$D$19*B7+$D$20</f>
+        <v>1.4602099380356033E-2</v>
+      </c>
+      <c r="E7">
+        <f>$D$21/(B7+$D$22)-$D$18</f>
+        <v>61.483303253317374</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A8">
+        <v>70</v>
+      </c>
+      <c r="B8">
+        <v>88</v>
+      </c>
+      <c r="C8">
+        <f>1/(A8+$D$18)</f>
+        <v>1.2987012987012988E-2</v>
+      </c>
+      <c r="D8">
+        <f>$D$19*B8+$D$20</f>
+        <v>1.3318542387216645E-2</v>
+      </c>
+      <c r="E8">
+        <f>$D$21/(B8+$D$22)-$D$18</f>
+        <v>68.083291468878485</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A9">
+        <v>80</v>
+      </c>
+      <c r="B9">
+        <v>74</v>
+      </c>
+      <c r="C9">
+        <f>1/(A9+$D$18)</f>
+        <v>1.1494252873563218E-2</v>
+      </c>
+      <c r="D9">
+        <f>$D$19*B9+$D$20</f>
+        <v>1.1521562596821503E-2</v>
+      </c>
+      <c r="E9">
+        <f>$D$21/(B9+$D$22)-$D$18</f>
+        <v>79.79378266589238</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B10" s="3"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B11" s="3"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B12" s="3"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B13" s="3"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B14" s="3"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B15" s="3"/>
+    </row>
+    <row r="18" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C19" t="s">
+        <v>2</v>
+      </c>
+      <c r="D19">
+        <f>(C3-C9)/(B3-B9)</f>
+        <v>1.2835569931393879E-4</v>
+      </c>
+    </row>
+    <row r="20" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C20" t="s">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <f>C5-(D19*B5)</f>
+        <v>2.0232408475900319E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C21" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21">
+        <f>1/D19</f>
+        <v>7790.85</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C22" t="s">
+        <v>5</v>
+      </c>
+      <c r="D22">
+        <f>D20/D19</f>
+        <v>15.762765957446801</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C24" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C26" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
